--- a/data/trans_orig/P63-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P63-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220833</t>
+          <t>219744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249296</t>
+          <t>248411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246755</t>
+          <t>247420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290881</t>
+          <t>289817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>476397</t>
+          <t>477983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>531051</t>
+          <t>532231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>87219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240096</t>
+          <t>241160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284222</t>
+          <t>283557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306889</t>
+          <t>305709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>361543</t>
+          <t>359957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>296230</t>
+          <t>297782</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329345</t>
+          <t>332751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312327</t>
+          <t>310027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>365709</t>
+          <t>364616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>620241</t>
+          <t>618268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>685594</t>
+          <t>684999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>102995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334958</t>
+          <t>336051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388340</t>
+          <t>390640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415850</t>
+          <t>416445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481203</t>
+          <t>483176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217965</t>
+          <t>218665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241398</t>
+          <t>241484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183244</t>
+          <t>185387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226686</t>
+          <t>228997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>411209</t>
+          <t>410286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461244</t>
+          <t>462663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242125</t>
+          <t>239814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285567</t>
+          <t>283424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>278656</t>
+          <t>277237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328691</t>
+          <t>329614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264794</t>
+          <t>265481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298992</t>
+          <t>299356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>262121</t>
+          <t>259884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311733</t>
+          <t>313237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>542163</t>
+          <t>537141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>605112</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85594</t>
+          <t>85230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119792</t>
+          <t>119105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336746</t>
+          <t>335242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386358</t>
+          <t>388595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427952</t>
+          <t>432562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490901</t>
+          <t>495923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1032624</t>
+          <t>1034857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1092730</t>
+          <t>1096006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1053538</t>
+          <t>1052363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1148063</t>
+          <t>1149567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2106175</t>
+          <t>2108241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2228177</t>
+          <t>2224077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330791</t>
+          <t>328558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1200871</t>
+          <t>1199367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1295396</t>
+          <t>1296571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1484172</t>
+          <t>1488272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1606174</t>
+          <t>1604108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373544</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398939</t>
+          <t>397945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>304964</t>
+          <t>302365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>350534</t>
+          <t>349893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687603</t>
+          <t>684382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>741442</t>
+          <t>742642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>34578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182295</t>
+          <t>182936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227865</t>
+          <t>230464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223910</t>
+          <t>222710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277749</t>
+          <t>280970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511001</t>
+          <t>510279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543387</t>
+          <t>542856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435361</t>
+          <t>434912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>492166</t>
+          <t>491268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>956960</t>
+          <t>958686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1022990</t>
+          <t>1024354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63869</t>
+          <t>64400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96255</t>
+          <t>96977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262423</t>
+          <t>263321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319228</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338855</t>
+          <t>337491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404885</t>
+          <t>403159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>363675</t>
+          <t>362945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>391980</t>
+          <t>393684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>267699</t>
+          <t>269461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318418</t>
+          <t>318946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>639054</t>
+          <t>640764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>701812</t>
+          <t>702633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42290</t>
+          <t>40586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70595</t>
+          <t>71325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242282</t>
+          <t>241754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293001</t>
+          <t>291239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293158</t>
+          <t>292337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355916</t>
+          <t>354206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>416796</t>
+          <t>416889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451027</t>
+          <t>450560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>376603</t>
+          <t>375377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>430124</t>
+          <t>429922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>803718</t>
+          <t>803976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>872527</t>
+          <t>872637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105139</t>
+          <t>105046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317161</t>
+          <t>317363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370682</t>
+          <t>371908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396692</t>
+          <t>396582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>465501</t>
+          <t>465243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1696224</t>
+          <t>1698001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1758590</t>
+          <t>1755582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1433281</t>
+          <t>1434320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1535756</t>
+          <t>1535416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3155172</t>
+          <t>3146761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3284902</t>
+          <t>3278176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237393</t>
+          <t>240401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299759</t>
+          <t>297982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1059647</t>
+          <t>1059987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1162122</t>
+          <t>1161083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1306484</t>
+          <t>1313210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1436214</t>
+          <t>1444625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364202</t>
+          <t>363009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392213</t>
+          <t>391545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>273414</t>
+          <t>274181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317911</t>
+          <t>318221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>644322</t>
+          <t>646118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>700317</t>
+          <t>700698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>39964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67307</t>
+          <t>68500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186590</t>
+          <t>186280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231087</t>
+          <t>230320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235694</t>
+          <t>235313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291689</t>
+          <t>289893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>508828</t>
+          <t>510767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543474</t>
+          <t>544134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439836</t>
+          <t>435722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>493221</t>
+          <t>492204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>960258</t>
+          <t>959638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1028254</t>
+          <t>1026511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>62785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98091</t>
+          <t>96152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271560</t>
+          <t>272577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324945</t>
+          <t>329059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343446</t>
+          <t>345189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411442</t>
+          <t>412062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>312512</t>
+          <t>313954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342411</t>
+          <t>342915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247319</t>
+          <t>247407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293223</t>
+          <t>293442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>569115</t>
+          <t>567029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>629133</t>
+          <t>626666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>77800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217618</t>
+          <t>217399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263522</t>
+          <t>263434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273462</t>
+          <t>275929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333480</t>
+          <t>335566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423069</t>
+          <t>425480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>458509</t>
+          <t>458911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352970</t>
+          <t>353591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>407918</t>
+          <t>409644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>792110</t>
+          <t>789386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>857372</t>
+          <t>858486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76967</t>
+          <t>76565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112407</t>
+          <t>109996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307336</t>
+          <t>305610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362284</t>
+          <t>361663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393357</t>
+          <t>392243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458619</t>
+          <t>461343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1641647</t>
+          <t>1642828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1707558</t>
+          <t>1708648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1361163</t>
+          <t>1361597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1460841</t>
+          <t>1461381</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3028941</t>
+          <t>3026097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3155190</t>
+          <t>3157114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258099</t>
+          <t>257009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>324010</t>
+          <t>322829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1034536</t>
+          <t>1033996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1134214</t>
+          <t>1133780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1305844</t>
+          <t>1303920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1432093</t>
+          <t>1434937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023 (tasa de respuesta: 98,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228286</t>
+          <t>227030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271043</t>
+          <t>271117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>267495</t>
+          <t>268668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>298927</t>
+          <t>296846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>509694</t>
+          <t>508533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>560854</t>
+          <t>560293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>65774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114304</t>
+          <t>116385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145736</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145182</t>
+          <t>145743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196342</t>
+          <t>197503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>281819</t>
+          <t>282039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>327107</t>
+          <t>326995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>309110</t>
+          <t>308194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>348561</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>604243</t>
+          <t>605282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>662420</t>
+          <t>665845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>55145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100321</t>
+          <t>100101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>198329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240057</t>
+          <t>240973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>268887</t>
+          <t>265462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327064</t>
+          <t>326025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254416</t>
+          <t>254775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>302608</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>349216</t>
+          <t>352794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>543143</t>
+          <t>547760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>643826</t>
+          <t>649257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>825382</t>
+          <t>837944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>87113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252346</t>
+          <t>248768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118068</t>
+          <t>105506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299624</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339410</t>
+          <t>339498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>386043</t>
+          <t>386628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316239</t>
+          <t>314889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>357964</t>
+          <t>357583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>668180</t>
+          <t>670073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>731753</t>
+          <t>732805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46187</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92820</t>
+          <t>92732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230889</t>
+          <t>231270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272614</t>
+          <t>273964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289330</t>
+          <t>288278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>352903</t>
+          <t>351010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1161421</t>
+          <t>1159417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1250838</t>
+          <t>1249434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1296788</t>
+          <t>1291436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1580121</t>
+          <t>1604964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2512451</t>
+          <t>2513521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2789783</t>
+          <t>2788307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198223</t>
+          <t>199627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287640</t>
+          <t>289644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572692</t>
+          <t>547849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>856025</t>
+          <t>861377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>812092</t>
+          <t>813568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1089424</t>
+          <t>1088354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P63-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P63-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>219744</t>
+          <t>222595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248411</t>
+          <t>251153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247420</t>
+          <t>244452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289817</t>
+          <t>290174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>477983</t>
+          <t>477622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>532231</t>
+          <t>530725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>55810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87219</t>
+          <t>84368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241160</t>
+          <t>240803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283557</t>
+          <t>286525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305709</t>
+          <t>307215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359957</t>
+          <t>360318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>297782</t>
+          <t>298208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332751</t>
+          <t>331169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>310027</t>
+          <t>310518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>364616</t>
+          <t>364599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>618268</t>
+          <t>623409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>684999</t>
+          <t>688016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>69608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102995</t>
+          <t>102569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336051</t>
+          <t>336068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390640</t>
+          <t>390149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416445</t>
+          <t>413428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>483176</t>
+          <t>478035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>218665</t>
+          <t>219868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241484</t>
+          <t>242540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185387</t>
+          <t>184730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228997</t>
+          <t>227789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>410286</t>
+          <t>409774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>462663</t>
+          <t>463187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>51221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239814</t>
+          <t>241022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283424</t>
+          <t>284081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>276713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329614</t>
+          <t>330126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265481</t>
+          <t>267034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299356</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259884</t>
+          <t>262722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313237</t>
+          <t>313933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>537141</t>
+          <t>541628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>603141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85230</t>
+          <t>84490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119105</t>
+          <t>117552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335242</t>
+          <t>334546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>388595</t>
+          <t>385757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432562</t>
+          <t>429923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495923</t>
+          <t>491436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1034857</t>
+          <t>1037410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1096006</t>
+          <t>1097737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1049832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1149567</t>
+          <t>1146176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2108241</t>
+          <t>2105268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2224077</t>
+          <t>2228217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267409</t>
+          <t>265678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328558</t>
+          <t>326005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1199367</t>
+          <t>1202758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1296571</t>
+          <t>1299102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1488272</t>
+          <t>1484132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1604108</t>
+          <t>1607081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372735</t>
+          <t>373406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397945</t>
+          <t>399168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>302365</t>
+          <t>306097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>349893</t>
+          <t>350180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>684382</t>
+          <t>687517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>742642</t>
+          <t>743083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34578</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182936</t>
+          <t>182649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230464</t>
+          <t>226732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222710</t>
+          <t>222269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280970</t>
+          <t>277835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>510279</t>
+          <t>509487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>542856</t>
+          <t>542693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434912</t>
+          <t>431459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>491268</t>
+          <t>489934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>958686</t>
+          <t>955010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1024354</t>
+          <t>1026998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64400</t>
+          <t>64563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96977</t>
+          <t>97769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263321</t>
+          <t>264655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319677</t>
+          <t>323130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337491</t>
+          <t>334847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>403159</t>
+          <t>406835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362945</t>
+          <t>363022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>393684</t>
+          <t>392135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269461</t>
+          <t>267962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318946</t>
+          <t>315499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640764</t>
+          <t>636053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>702633</t>
+          <t>697494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>71248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241754</t>
+          <t>245201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291239</t>
+          <t>292738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292337</t>
+          <t>297476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354206</t>
+          <t>358917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>416889</t>
+          <t>418623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>450560</t>
+          <t>451500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>375377</t>
+          <t>374552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>429922</t>
+          <t>430180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>803976</t>
+          <t>803122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>872637</t>
+          <t>871424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>70435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105046</t>
+          <t>103312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317363</t>
+          <t>317105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371908</t>
+          <t>372733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396582</t>
+          <t>397795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>465243</t>
+          <t>466097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1698001</t>
+          <t>1692782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1755582</t>
+          <t>1755327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1434320</t>
+          <t>1436040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1535416</t>
+          <t>1537839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3146761</t>
+          <t>3147525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3278176</t>
+          <t>3275217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240401</t>
+          <t>240656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297982</t>
+          <t>303201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1059987</t>
+          <t>1057564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1161083</t>
+          <t>1159363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1313210</t>
+          <t>1316169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1444625</t>
+          <t>1443861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>363009</t>
+          <t>364627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>391545</t>
+          <t>391787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>274181</t>
+          <t>273611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318221</t>
+          <t>317963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646118</t>
+          <t>647725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>700698</t>
+          <t>704673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>39722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68500</t>
+          <t>66882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186280</t>
+          <t>186538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230320</t>
+          <t>230890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235313</t>
+          <t>231338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289893</t>
+          <t>288286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>510767</t>
+          <t>509794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>544134</t>
+          <t>543904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435722</t>
+          <t>437472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>492204</t>
+          <t>493698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>959638</t>
+          <t>959773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1026511</t>
+          <t>1027677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62785</t>
+          <t>63015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96152</t>
+          <t>97125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272577</t>
+          <t>271083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329059</t>
+          <t>327309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345189</t>
+          <t>344023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>412062</t>
+          <t>411927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>312000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342915</t>
+          <t>342400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247407</t>
+          <t>245754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293442</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567029</t>
+          <t>569928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626666</t>
+          <t>627645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>49354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77800</t>
+          <t>79754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217399</t>
+          <t>216668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263434</t>
+          <t>265087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275929</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335566</t>
+          <t>332667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>425480</t>
+          <t>422913</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>458911</t>
+          <t>458586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>353591</t>
+          <t>354538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>409644</t>
+          <t>410048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>789386</t>
+          <t>788181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>858486</t>
+          <t>856673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76565</t>
+          <t>76890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109996</t>
+          <t>112563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305610</t>
+          <t>305206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361663</t>
+          <t>360716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392243</t>
+          <t>394056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>461343</t>
+          <t>462548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1642828</t>
+          <t>1647772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1708648</t>
+          <t>1708749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1361597</t>
+          <t>1363543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1461381</t>
+          <t>1461270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3026097</t>
+          <t>3027509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3157114</t>
+          <t>3153572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>256908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322829</t>
+          <t>317885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1033996</t>
+          <t>1034107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1133780</t>
+          <t>1131834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1303920</t>
+          <t>1307462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1434937</t>
+          <t>1433525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>255677</t>
+          <t>279025</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227030</t>
+          <t>254846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271117</t>
+          <t>294145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>283481</t>
+          <t>304938</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268668</t>
+          <t>287956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296846</t>
+          <t>321280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>539159</t>
+          <t>583963</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508533</t>
+          <t>556353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>560293</t>
+          <t>606125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65774</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>143935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116385</t>
+          <t>127593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>166877</t>
+          <t>179254</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145743</t>
+          <t>157092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197503</t>
+          <t>206864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>292804</t>
+          <t>314344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>292804</t>
+          <t>314344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>292804</t>
+          <t>314344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>413231</t>
+          <t>448873</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413231</t>
+          <t>448873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>413231</t>
+          <t>448873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>706036</t>
+          <t>763217</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>706036</t>
+          <t>763217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>706036</t>
+          <t>763217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>306487</t>
+          <t>341575</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>282039</t>
+          <t>316150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>326995</t>
+          <t>362434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>329276</t>
+          <t>368552</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>308194</t>
+          <t>348037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350838</t>
+          <t>391162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>635762</t>
+          <t>710127</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>605282</t>
+          <t>677581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>665845</t>
+          <t>738468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75653</t>
+          <t>74579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>219891</t>
+          <t>245354</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198329</t>
+          <t>222744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240973</t>
+          <t>265869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>295545</t>
+          <t>319932</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265462</t>
+          <t>291591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326025</t>
+          <t>352478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>382140</t>
+          <t>416154</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>382140</t>
+          <t>416154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>382140</t>
+          <t>416154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>549167</t>
+          <t>613906</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>549167</t>
+          <t>613906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>549167</t>
+          <t>613906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>931307</t>
+          <t>1030059</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>931307</t>
+          <t>1030059</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>931307</t>
+          <t>1030059</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>281520</t>
+          <t>318491</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254775</t>
+          <t>292427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303745</t>
+          <t>338466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>442300</t>
+          <t>283219</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>352794</t>
+          <t>260004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>547760</t>
+          <t>302505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>723820</t>
+          <t>601711</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649257</t>
+          <t>569130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>837944</t>
+          <t>630809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>57152</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87113</t>
+          <t>83216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159262</t>
+          <t>179778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>160492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248768</t>
+          <t>202993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>219630</t>
+          <t>236929</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>207831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294193</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>341888</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341888</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>341888</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>601562</t>
+          <t>462997</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>601562</t>
+          <t>462997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>601562</t>
+          <t>462997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>943450</t>
+          <t>838640</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>943450</t>
+          <t>838640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>943450</t>
+          <t>838640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>364871</t>
+          <t>379680</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>339498</t>
+          <t>356430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>386628</t>
+          <t>400227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>336386</t>
+          <t>370982</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>314889</t>
+          <t>348393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>357583</t>
+          <t>392499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>701257</t>
+          <t>750662</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>670073</t>
+          <t>719487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732805</t>
+          <t>780454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45602</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>93428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>252467</t>
+          <t>275215</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231270</t>
+          <t>253698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273964</t>
+          <t>297804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>319826</t>
+          <t>345393</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288278</t>
+          <t>315601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351010</t>
+          <t>376568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>432230</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>432230</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>432230</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>588853</t>
+          <t>646197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>588853</t>
+          <t>646197</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>588853</t>
+          <t>646197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1021083</t>
+          <t>1096055</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1021083</t>
+          <t>1096055</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1021083</t>
+          <t>1096055</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1208554</t>
+          <t>1318771</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1159417</t>
+          <t>1274910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1249434</t>
+          <t>1359404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1391442</t>
+          <t>1327691</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1291436</t>
+          <t>1287488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1604964</t>
+          <t>1369894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2599997</t>
+          <t>2646462</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2513521</t>
+          <t>2585898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2788307</t>
+          <t>2706725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199627</t>
+          <t>196595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289644</t>
+          <t>281089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547849</t>
+          <t>802078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>861377</t>
+          <t>884484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813568</t>
+          <t>1021246</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1088354</t>
+          <t>1142073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
